--- a/forms/trg/Formulir_TRG_nutritionmdp.xlsx
+++ b/forms/trg/Formulir_TRG_nutritionmdp.xlsx
@@ -554,7 +554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -698,126 +698,114 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>ID peneliti (SINTA/Scopus/ORCID) banyak yang kosong.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>3.</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
           <t>Belum ada artikel tercatat di situs. Mohon cantumkan riset terbaik di lembar TRG &amp; Riset.</t>
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Contoh pengisian (hanya ilustrasi, jangan disalin)</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>Contoh pengisian (hanya ilustrasi, jangan disalin)</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Nama</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>Dr. Contoh Nama, S.Pi., M.Si.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Nama</t>
+          <t>Keahlian utama 1-3 (pilih)</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>Dr. Contoh Nama, S.Pi., M.Si.</t>
+          <t>Perikanan &amp; akuakultur; Ekosistem pesisir &amp; laut</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>Keahlian utama 1-3 (pilih)</t>
+          <t>Kata kunci keahlian</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Perikanan &amp; akuakultur; Ekosistem pesisir &amp; laut</t>
+          <t>budidaya udang, kualitas air, bioflok</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Kata kunci keahlian</t>
+          <t>SINTA ID</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>budidaya udang, kualitas air, bioflok</t>
+          <t>6012345</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>SINTA ID</t>
+          <t>ORCID</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>6012345</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>ORCID</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
           <t>0000-0002-1234-5678</t>
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Kemajuan pengisian (otomatis)</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>Kemajuan pengisian (otomatis)</t>
-        </is>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Anggota tercantum</t>
+        </is>
+      </c>
+      <c r="B25" s="7">
+        <f>COUNTA(Anggota!B5:B31)</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>Anggota tercantum</t>
+          <t>Anggota dengan keahlian terpilih</t>
         </is>
       </c>
       <c r="B26" s="7">
-        <f>COUNTA(Anggota!B5:B30)</f>
+        <f>COUNTA(Anggota!F5:F31)</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Anggota dengan keahlian terpilih</t>
-        </is>
-      </c>
-      <c r="B27" s="7">
-        <f>COUNTA(Anggota!F5:F30)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
           <t>Persentase anggota berkeahlian</t>
         </is>
       </c>
-      <c r="B28" s="8">
-        <f>IF(B26=0,0,B27/B26)</f>
+      <c r="B27" s="8">
+        <f>IF(B25=0,0,B26/B25)</f>
         <v/>
       </c>
     </row>
@@ -832,7 +820,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -937,31 +925,39 @@
       </c>
       <c r="B5" s="11" t="inlineStr">
         <is>
-          <t>Irmayanti, S.Gz.,M.PH.</t>
+          <t>Prof. Dr. Nurhaedar Jafar, Apt.,M.Kes</t>
         </is>
       </c>
       <c r="C5" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
-        </is>
-      </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Leader</t>
+        </is>
+      </c>
+      <c r="D5" s="12" t="n"/>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Nutrition Survey</t>
+          <t>Nutrition and Metabolic Disease</t>
         </is>
       </c>
       <c r="F5" s="12" t="n"/>
       <c r="G5" s="12" t="n"/>
       <c r="H5" s="12" t="n"/>
       <c r="I5" s="12" t="n"/>
-      <c r="J5" s="12" t="n"/>
-      <c r="K5" s="12" t="n"/>
-      <c r="L5" s="12" t="n"/>
+      <c r="J5" s="11" t="inlineStr">
+        <is>
+          <t>0000-0003-1578-0831</t>
+        </is>
+      </c>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>6011613</t>
+        </is>
+      </c>
+      <c r="L5" s="11" t="inlineStr">
+        <is>
+          <t>57199699117</t>
+        </is>
+      </c>
       <c r="M5" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -974,38 +970,30 @@
       </c>
       <c r="B6" s="11" t="inlineStr">
         <is>
-          <t>Prof. Dr. Aminuddin Syam, SKM.,M.Kes</t>
+          <t>Irmayanti, S.Gz.,M.PH.</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>Department of Nutrition Science, Faculty of Public Health, Hasanuddin University</t>
+          <t>Hasanuddin University</t>
         </is>
       </c>
       <c r="E6" s="11" t="inlineStr">
         <is>
-          <t>Functional food for nutritional deficiency</t>
+          <t>Nutrition Survey</t>
         </is>
       </c>
       <c r="F6" s="12" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="12" t="n"/>
       <c r="I6" s="12" t="n"/>
-      <c r="J6" s="11" t="inlineStr">
-        <is>
-          <t>http://https//orcid.org/0000-0001-7284-2985</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>6004882</t>
-        </is>
-      </c>
+      <c r="J6" s="12" t="n"/>
+      <c r="K6" s="12" t="n"/>
       <c r="L6" s="12" t="n"/>
       <c r="M6" s="11" t="inlineStr">
         <is>
@@ -1019,12 +1007,12 @@
       </c>
       <c r="B7" s="11" t="inlineStr">
         <is>
-          <t>Dr. Healthy Hidayanty, SKM.M.Kes</t>
+          <t>Prof. Dr. Aminuddin Syam, SKM.,M.Kes</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -1034,7 +1022,7 @@
       </c>
       <c r="E7" s="11" t="inlineStr">
         <is>
-          <t>Nutritional anthropology</t>
+          <t>Functional food for nutritional deficiency</t>
         </is>
       </c>
       <c r="F7" s="12" t="n"/>
@@ -1043,12 +1031,12 @@
       <c r="I7" s="12" t="n"/>
       <c r="J7" s="11" t="inlineStr">
         <is>
-          <t>0000-0003-4319-0011</t>
+          <t>http://https//orcid.org/0000-0001-7284-2985</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
         <is>
-          <t>6654764</t>
+          <t>6004882</t>
         </is>
       </c>
       <c r="L7" s="12" t="n"/>
@@ -1064,12 +1052,12 @@
       </c>
       <c r="B8" s="11" t="inlineStr">
         <is>
-          <t>Dr.dr. Anna Khuzaimah, M.Kes</t>
+          <t>Dr. Healthy Hidayanty, SKM.M.Kes</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
         <is>
-          <t>Lecturers</t>
+          <t>Lecturer</t>
         </is>
       </c>
       <c r="D8" s="11" t="inlineStr">
@@ -1079,7 +1067,7 @@
       </c>
       <c r="E8" s="11" t="inlineStr">
         <is>
-          <t>Traditional and Herbal medicine</t>
+          <t>Nutritional anthropology</t>
         </is>
       </c>
       <c r="F8" s="12" t="n"/>
@@ -1088,19 +1076,15 @@
       <c r="I8" s="12" t="n"/>
       <c r="J8" s="11" t="inlineStr">
         <is>
-          <t>0009-0006-2729-643X</t>
+          <t>0000-0003-4319-0011</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
-          <t>6875311</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="inlineStr">
-        <is>
-          <t>59318713700</t>
-        </is>
-      </c>
+          <t>6654764</t>
+        </is>
+      </c>
+      <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1113,23 +1097,43 @@
       </c>
       <c r="B9" s="11" t="inlineStr">
         <is>
-          <t>Assoc Prof. Dr Foo Leng Huat</t>
+          <t>Dr.dr. Anna Khuzaimah, M.Kes</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>External Collaborators</t>
-        </is>
-      </c>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="11" t="n"/>
+          <t>Lecturer</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t>Department of Nutrition Science, Faculty of Public Health, Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E9" s="11" t="inlineStr">
+        <is>
+          <t>Traditional and Herbal medicine</t>
+        </is>
+      </c>
       <c r="F9" s="12" t="n"/>
       <c r="G9" s="12" t="n"/>
       <c r="H9" s="12" t="n"/>
       <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
+      <c r="J9" s="11" t="inlineStr">
+        <is>
+          <t>0009-0006-2729-643X</t>
+        </is>
+      </c>
+      <c r="K9" s="11" t="inlineStr">
+        <is>
+          <t>6875311</t>
+        </is>
+      </c>
+      <c r="L9" s="11" t="inlineStr">
+        <is>
+          <t>59318713700</t>
+        </is>
+      </c>
       <c r="M9" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1142,39 +1146,23 @@
       </c>
       <c r="B10" s="11" t="inlineStr">
         <is>
-          <t>Yessy Kurniati, SKM, M.Kes</t>
+          <t>Assoc Prof. Dr Foo Leng Huat</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
-          <t>Researchers</t>
-        </is>
-      </c>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>UIN Alauddin</t>
-        </is>
-      </c>
-      <c r="E10" s="11" t="inlineStr">
-        <is>
-          <t>Nutrition Education</t>
-        </is>
-      </c>
+          <t>External collaborator</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="11" t="n"/>
       <c r="F10" s="12" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="12" t="n"/>
       <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
-      <c r="K10" s="11" t="inlineStr">
-        <is>
-          <t>6707075</t>
-        </is>
-      </c>
-      <c r="L10" s="11" t="inlineStr">
-        <is>
-          <t>57202649790</t>
-        </is>
-      </c>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="12" t="n"/>
       <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1187,23 +1175,39 @@
       </c>
       <c r="B11" s="11" t="inlineStr">
         <is>
-          <t>Dewi Purnama Windasari</t>
+          <t>Yessy Kurniati, SKM, M.Kes</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="n"/>
-      <c r="E11" s="11" t="n"/>
+          <t>Researcher</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>UIN Alauddin</t>
+        </is>
+      </c>
+      <c r="E11" s="11" t="inlineStr">
+        <is>
+          <t>Nutrition Education</t>
+        </is>
+      </c>
       <c r="F11" s="12" t="n"/>
       <c r="G11" s="12" t="n"/>
       <c r="H11" s="12" t="n"/>
       <c r="I11" s="12" t="n"/>
       <c r="J11" s="12" t="n"/>
-      <c r="K11" s="12" t="n"/>
-      <c r="L11" s="12" t="n"/>
+      <c r="K11" s="11" t="inlineStr">
+        <is>
+          <t>6707075</t>
+        </is>
+      </c>
+      <c r="L11" s="11" t="inlineStr">
+        <is>
+          <t>57202649790</t>
+        </is>
+      </c>
       <c r="M11" s="11" t="inlineStr">
         <is>
           <t>Aktif</t>
@@ -1216,12 +1220,12 @@
       </c>
       <c r="B12" s="11" t="inlineStr">
         <is>
-          <t>Zahrah Ramadani</t>
+          <t>Dewi Purnama Windasari</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D12" s="12" t="n"/>
@@ -1245,19 +1249,15 @@
       </c>
       <c r="B13" s="11" t="inlineStr">
         <is>
-          <t>Fatimah Kautsar</t>
+          <t>Zahrah Ramadani</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
-        </is>
-      </c>
-      <c r="D13" s="11" t="inlineStr">
-        <is>
-          <t>Hasanuddin University</t>
-        </is>
-      </c>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n"/>
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="12" t="n"/>
       <c r="G13" s="12" t="n"/>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B14" s="11" t="inlineStr">
         <is>
-          <t>Agung Perdana</t>
+          <t>Fatimah Kautsar</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D14" s="11" t="inlineStr">
@@ -1311,12 +1311,12 @@
       </c>
       <c r="B15" s="11" t="inlineStr">
         <is>
-          <t>Ainun Jariah</t>
+          <t>Agung Perdana</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D15" s="11" t="inlineStr">
@@ -1344,12 +1344,12 @@
       </c>
       <c r="B16" s="11" t="inlineStr">
         <is>
-          <t>Junedi Sitorus</t>
+          <t>Ainun Jariah</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B17" s="11" t="inlineStr">
         <is>
-          <t>Sri Ulandari</t>
+          <t>Junedi Sitorus</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D17" s="11" t="inlineStr">
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B18" s="11" t="inlineStr">
         <is>
-          <t>Rouzatunnisa</t>
+          <t>Sri Ulandari</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
         <is>
-          <t>Students</t>
+          <t>Student</t>
         </is>
       </c>
       <c r="D18" s="11" t="inlineStr">
@@ -1441,10 +1441,26 @@
       <c r="A19" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="11" t="n"/>
+      <c r="B19" s="11" t="inlineStr">
+        <is>
+          <t>Rouzatunnisa</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="inlineStr">
+        <is>
+          <t>Student</t>
+        </is>
+      </c>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Hasanuddin University</t>
+        </is>
+      </c>
+      <c r="E19" s="11" t="inlineStr">
+        <is>
+          <t>Welcome to our website. We are a research group that studies the potential of food to prevent metabolic disease. On this website, we present information about the theme and focus of research, research teams, research activities that we have carried out and are currently carrying out, as well as various publications, including books, patents and scientific articles. We hope that this website will benefit the wider community</t>
+        </is>
+      </c>
       <c r="F19" s="12" t="n"/>
       <c r="G19" s="12" t="n"/>
       <c r="H19" s="12" t="n"/>
@@ -1452,7 +1468,11 @@
       <c r="J19" s="12" t="n"/>
       <c r="K19" s="12" t="n"/>
       <c r="L19" s="12" t="n"/>
-      <c r="M19" s="12" t="n"/>
+      <c r="M19" s="11" t="inlineStr">
+        <is>
+          <t>Aktif</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -1641,15 +1661,32 @@
       <c r="L30" s="12" t="n"/>
       <c r="M30" s="12" t="n"/>
     </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <dataValidations count="2">
-    <dataValidation sqref="F5:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="F5:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$A$2:$A$39</formula1>
     </dataValidation>
-    <dataValidation sqref="M5:M30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M5:M31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>=Daftar!$C$2:$C$3</formula1>
     </dataValidation>
   </dataValidations>
